--- a/exams/CSE/22.08.26_Seat_Details_Merged.xlsx
+++ b/exams/CSE/22.08.26_Seat_Details_Merged.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsfgafgjg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD34F968-5594-4118-9E1A-A55A0B7F19D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D58A459-24F3-4BD3-BB22-68B87BE3B535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -1689,6 +1689,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -1700,6 +1703,7 @@
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1884,9 +1888,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1928,6 +1929,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2595,25 +2599,25 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="31">
         <v>46256</v>
       </c>
       <c r="C2" t="s">
         <v>169</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -2622,68 +2626,68 @@
       <c r="I2" s="8">
         <v>14</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A3" s="25"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="8">
         <v>14</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="25"/>
     </row>
     <row r="4" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A4" s="25"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="8">
         <v>14</v>
       </c>
-      <c r="J4" s="26"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A5" s="25"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="8">
         <v>9</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A6" s="25"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="18" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2692,84 +2696,84 @@
       <c r="I6" s="8">
         <v>5</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A7" s="25"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="8">
         <v>14</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="25"/>
     </row>
     <row r="8" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A8" s="25"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="8">
         <v>14</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="25"/>
     </row>
     <row r="9" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A9" s="25"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="8">
         <v>14</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="25"/>
     </row>
     <row r="10" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A10" s="25"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
       <c r="H10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="8">
         <v>4</v>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A11" s="25"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="18" t="s">
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="17" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -2778,68 +2782,68 @@
       <c r="I11" s="8">
         <v>10</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A12" s="25"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="8">
         <v>14</v>
       </c>
-      <c r="J12" s="26"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A13" s="25"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="8">
         <v>14</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A14" s="25"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
       <c r="H14" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="8">
         <v>13</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A15" s="25"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="18" t="s">
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="17" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -2848,84 +2852,84 @@
       <c r="I15" s="8">
         <v>1</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A16" s="25"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="8">
         <v>14</v>
       </c>
-      <c r="J16" s="26"/>
+      <c r="J16" s="25"/>
     </row>
     <row r="17" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A17" s="25"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I17" s="8">
         <v>14</v>
       </c>
-      <c r="J17" s="26"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A18" s="25"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="8">
         <v>14</v>
       </c>
-      <c r="J18" s="26"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A19" s="25"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I19" s="8">
         <v>8</v>
       </c>
-      <c r="J19" s="21"/>
+      <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A20" s="25"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="18" t="s">
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="17" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -2934,84 +2938,84 @@
       <c r="I20" s="8">
         <v>6</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A21" s="25"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="8">
         <v>14</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A22" s="25"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="8">
         <v>14</v>
       </c>
-      <c r="J22" s="26"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A23" s="25"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
       <c r="H23" s="4" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="8">
         <v>14</v>
       </c>
-      <c r="J23" s="26"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A24" s="25"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
       <c r="H24" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I24" s="8">
         <v>3</v>
       </c>
-      <c r="J24" s="21"/>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A25" s="25"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="18" t="s">
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="17" t="s">
         <v>34</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -3020,52 +3024,52 @@
       <c r="I25" s="8">
         <v>11</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A26" s="25"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
       <c r="H26" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I26" s="8">
         <v>14</v>
       </c>
-      <c r="J26" s="26"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A27" s="25"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
       <c r="H27" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I27" s="8">
         <v>26</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A28" s="25"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="18" t="s">
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="17" t="s">
         <v>38</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -3074,36 +3078,36 @@
       <c r="I28" s="8">
         <v>14</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="19">
         <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A29" s="25"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
       <c r="H29" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I29" s="8">
         <v>35</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A30" s="25"/>
+      <c r="A30" s="24"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="18" t="s">
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="17" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -3112,68 +3116,68 @@
       <c r="I30" s="8">
         <v>1</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A31" s="25"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
       <c r="H31" s="8">
         <v>216</v>
       </c>
       <c r="I31" s="8">
         <v>24</v>
       </c>
-      <c r="J31" s="26"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A32" s="25"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
       <c r="H32" s="8">
         <v>217</v>
       </c>
       <c r="I32" s="8">
         <v>24</v>
       </c>
-      <c r="J32" s="26"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A33" s="19"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
       <c r="H33" s="8">
         <v>218</v>
       </c>
       <c r="I33" s="8">
         <v>2</v>
       </c>
-      <c r="J33" s="21"/>
+      <c r="J33" s="20"/>
     </row>
     <row r="34" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A34" s="27"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="18" t="s">
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="17" t="s">
         <v>42</v>
       </c>
       <c r="H34" s="8">
@@ -3182,52 +3186,52 @@
       <c r="I34" s="8">
         <v>22</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="19">
         <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A35" s="28"/>
+      <c r="A35" s="27"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
       <c r="H35" s="8">
         <v>219</v>
       </c>
       <c r="I35" s="8">
         <v>24</v>
       </c>
-      <c r="J35" s="26"/>
+      <c r="J35" s="25"/>
     </row>
     <row r="36" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A36" s="28"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
       <c r="H36" s="8">
         <v>220</v>
       </c>
       <c r="I36" s="8">
         <v>3</v>
       </c>
-      <c r="J36" s="21"/>
+      <c r="J36" s="20"/>
     </row>
     <row r="37" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A37" s="28"/>
+      <c r="A37" s="27"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="18" t="s">
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="17" t="s">
         <v>44</v>
       </c>
       <c r="H37" s="8">
@@ -3236,52 +3240,52 @@
       <c r="I37" s="8">
         <v>21</v>
       </c>
-      <c r="J37" s="20">
+      <c r="J37" s="19">
         <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A38" s="28"/>
+      <c r="A38" s="27"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
       <c r="H38" s="8">
         <v>221</v>
       </c>
       <c r="I38" s="8">
         <v>24</v>
       </c>
-      <c r="J38" s="26"/>
+      <c r="J38" s="25"/>
     </row>
     <row r="39" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A39" s="28"/>
+      <c r="A39" s="27"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
       <c r="H39" s="8">
         <v>222</v>
       </c>
       <c r="I39" s="8">
         <v>7</v>
       </c>
-      <c r="J39" s="21"/>
+      <c r="J39" s="20"/>
     </row>
     <row r="40" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A40" s="28"/>
+      <c r="A40" s="27"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="18" t="s">
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="17" t="s">
         <v>46</v>
       </c>
       <c r="H40" s="8">
@@ -3290,52 +3294,52 @@
       <c r="I40" s="8">
         <v>17</v>
       </c>
-      <c r="J40" s="20">
+      <c r="J40" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A41" s="28"/>
+      <c r="A41" s="27"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
       <c r="H41" s="8">
         <v>223</v>
       </c>
       <c r="I41" s="8">
         <v>24</v>
       </c>
-      <c r="J41" s="26"/>
+      <c r="J41" s="25"/>
     </row>
     <row r="42" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A42" s="28"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
       <c r="H42" s="8">
         <v>224</v>
       </c>
       <c r="I42" s="8">
         <v>10</v>
       </c>
-      <c r="J42" s="21"/>
+      <c r="J42" s="20"/>
     </row>
     <row r="43" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A43" s="28"/>
+      <c r="A43" s="27"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="18" t="s">
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G43" s="17" t="s">
         <v>47</v>
       </c>
       <c r="H43" s="8">
@@ -3344,52 +3348,52 @@
       <c r="I43" s="8">
         <v>14</v>
       </c>
-      <c r="J43" s="20">
+      <c r="J43" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A44" s="28"/>
+      <c r="A44" s="27"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
       <c r="H44" s="8">
         <v>303</v>
       </c>
       <c r="I44" s="8">
         <v>24</v>
       </c>
-      <c r="J44" s="26"/>
+      <c r="J44" s="25"/>
     </row>
     <row r="45" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A45" s="28"/>
+      <c r="A45" s="27"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
       <c r="H45" s="8">
         <v>304</v>
       </c>
       <c r="I45" s="8">
         <v>13</v>
       </c>
-      <c r="J45" s="21"/>
+      <c r="J45" s="20"/>
     </row>
     <row r="46" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A46" s="28"/>
+      <c r="A46" s="27"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="18" t="s">
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G46" s="18" t="s">
+      <c r="G46" s="17" t="s">
         <v>48</v>
       </c>
       <c r="H46" s="8">
@@ -3398,52 +3402,52 @@
       <c r="I46" s="8">
         <v>11</v>
       </c>
-      <c r="J46" s="20">
+      <c r="J46" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A47" s="28"/>
+      <c r="A47" s="27"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
       <c r="H47" s="8">
         <v>305</v>
       </c>
       <c r="I47" s="8">
         <v>24</v>
       </c>
-      <c r="J47" s="26"/>
+      <c r="J47" s="25"/>
     </row>
     <row r="48" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A48" s="28"/>
+      <c r="A48" s="27"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
       <c r="H48" s="8">
         <v>306</v>
       </c>
       <c r="I48" s="8">
         <v>16</v>
       </c>
-      <c r="J48" s="21"/>
+      <c r="J48" s="20"/>
     </row>
     <row r="49" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A49" s="28"/>
+      <c r="A49" s="27"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="18" t="s">
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="G49" s="18" t="s">
+      <c r="G49" s="17" t="s">
         <v>50</v>
       </c>
       <c r="H49" s="8">
@@ -3452,52 +3456,52 @@
       <c r="I49" s="8">
         <v>8</v>
       </c>
-      <c r="J49" s="20">
+      <c r="J49" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A50" s="28"/>
+      <c r="A50" s="27"/>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
       <c r="H50" s="8">
         <v>307</v>
       </c>
       <c r="I50" s="8">
         <v>28</v>
       </c>
-      <c r="J50" s="26"/>
+      <c r="J50" s="25"/>
     </row>
     <row r="51" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A51" s="28"/>
+      <c r="A51" s="27"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
       <c r="H51" s="4" t="s">
         <v>51</v>
       </c>
       <c r="I51" s="8">
         <v>15</v>
       </c>
-      <c r="J51" s="21"/>
+      <c r="J51" s="20"/>
     </row>
     <row r="52" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A52" s="28"/>
+      <c r="A52" s="27"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="18" t="s">
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="18" t="s">
+      <c r="G52" s="17" t="s">
         <v>53</v>
       </c>
       <c r="H52" s="4" t="s">
@@ -3506,52 +3510,52 @@
       <c r="I52" s="8">
         <v>9</v>
       </c>
-      <c r="J52" s="20">
+      <c r="J52" s="19">
         <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A53" s="28"/>
+      <c r="A53" s="27"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
       <c r="H53" s="4" t="s">
         <v>54</v>
       </c>
       <c r="I53" s="8">
         <v>24</v>
       </c>
-      <c r="J53" s="26"/>
+      <c r="J53" s="25"/>
     </row>
     <row r="54" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A54" s="28"/>
+      <c r="A54" s="27"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
       <c r="H54" s="8">
         <v>320</v>
       </c>
       <c r="I54" s="8">
         <v>19</v>
       </c>
-      <c r="J54" s="21"/>
+      <c r="J54" s="20"/>
     </row>
     <row r="55" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A55" s="28"/>
+      <c r="A55" s="27"/>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="18" t="s">
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G55" s="18" t="s">
+      <c r="G55" s="17" t="s">
         <v>56</v>
       </c>
       <c r="H55" s="8">
@@ -3560,42 +3564,42 @@
       <c r="I55" s="8">
         <v>28</v>
       </c>
-      <c r="J55" s="20">
+      <c r="J55" s="19">
         <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A56" s="29"/>
+      <c r="A56" s="28"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
       <c r="H56" s="4" t="s">
         <v>57</v>
       </c>
       <c r="I56" s="8">
         <v>24</v>
       </c>
-      <c r="J56" s="21"/>
+      <c r="J56" s="20"/>
     </row>
     <row r="57" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="18" t="s">
+      <c r="F57" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G57" s="18" t="s">
+      <c r="G57" s="17" t="s">
         <v>61</v>
       </c>
       <c r="H57" s="4" t="s">
@@ -3604,84 +3608,84 @@
       <c r="I57" s="8">
         <v>11</v>
       </c>
-      <c r="J57" s="20">
+      <c r="J57" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A58" s="25"/>
+      <c r="A58" s="24"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
       <c r="H58" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I58" s="8">
         <v>11</v>
       </c>
-      <c r="J58" s="26"/>
+      <c r="J58" s="25"/>
     </row>
     <row r="59" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A59" s="25"/>
+      <c r="A59" s="24"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
       <c r="H59" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I59" s="8">
         <v>11</v>
       </c>
-      <c r="J59" s="26"/>
+      <c r="J59" s="25"/>
     </row>
     <row r="60" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A60" s="25"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
       <c r="H60" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I60" s="8">
         <v>11</v>
       </c>
-      <c r="J60" s="26"/>
+      <c r="J60" s="25"/>
     </row>
     <row r="61" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A61" s="25"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
       <c r="H61" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="8">
         <v>6</v>
       </c>
-      <c r="J61" s="21"/>
+      <c r="J61" s="20"/>
     </row>
     <row r="62" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A62" s="25"/>
+      <c r="A62" s="24"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="18" t="s">
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G62" s="18" t="s">
+      <c r="G62" s="17" t="s">
         <v>62</v>
       </c>
       <c r="H62" s="4" t="s">
@@ -3690,84 +3694,84 @@
       <c r="I62" s="8">
         <v>5</v>
       </c>
-      <c r="J62" s="20">
+      <c r="J62" s="19">
         <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A63" s="25"/>
+      <c r="A63" s="24"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
       <c r="H63" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I63" s="8">
         <v>11</v>
       </c>
-      <c r="J63" s="26"/>
+      <c r="J63" s="25"/>
     </row>
     <row r="64" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A64" s="25"/>
+      <c r="A64" s="24"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
       <c r="H64" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I64" s="8">
         <v>11</v>
       </c>
-      <c r="J64" s="26"/>
+      <c r="J64" s="25"/>
     </row>
     <row r="65" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A65" s="25"/>
+      <c r="A65" s="24"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
       <c r="H65" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I65" s="8">
         <v>11</v>
       </c>
-      <c r="J65" s="26"/>
+      <c r="J65" s="25"/>
     </row>
     <row r="66" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A66" s="19"/>
+      <c r="A66" s="18"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
       <c r="H66" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I66" s="8">
         <v>6</v>
       </c>
-      <c r="J66" s="21"/>
+      <c r="J66" s="20"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="27"/>
+      <c r="A67" s="26"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="18" t="s">
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G67" s="18" t="s">
+      <c r="G67" s="17" t="s">
         <v>64</v>
       </c>
       <c r="H67" s="4" t="s">
@@ -3776,84 +3780,84 @@
       <c r="I67" s="8">
         <v>5</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="19">
         <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="28"/>
+      <c r="A68" s="27"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
       <c r="H68" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I68" s="8">
         <v>11</v>
       </c>
-      <c r="J68" s="26"/>
+      <c r="J68" s="25"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="28"/>
+      <c r="A69" s="27"/>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
       <c r="H69" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I69" s="8">
         <v>11</v>
       </c>
-      <c r="J69" s="26"/>
+      <c r="J69" s="25"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="28"/>
+      <c r="A70" s="27"/>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
       <c r="H70" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I70" s="8">
         <v>11</v>
       </c>
-      <c r="J70" s="26"/>
+      <c r="J70" s="25"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="28"/>
+      <c r="A71" s="27"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
       <c r="H71" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I71" s="8">
         <v>11</v>
       </c>
-      <c r="J71" s="21"/>
+      <c r="J71" s="20"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="28"/>
+      <c r="A72" s="27"/>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="18" t="s">
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G72" s="18" t="s">
+      <c r="G72" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H72" s="4" t="s">
@@ -3862,84 +3866,84 @@
       <c r="I72" s="8">
         <v>11</v>
       </c>
-      <c r="J72" s="20">
+      <c r="J72" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="28"/>
+      <c r="A73" s="27"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
       <c r="H73" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I73" s="8">
         <v>11</v>
       </c>
-      <c r="J73" s="26"/>
+      <c r="J73" s="25"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="28"/>
+      <c r="A74" s="27"/>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
       <c r="H74" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I74" s="8">
         <v>11</v>
       </c>
-      <c r="J74" s="26"/>
+      <c r="J74" s="25"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="28"/>
+      <c r="A75" s="27"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
       <c r="H75" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I75" s="8">
         <v>11</v>
       </c>
-      <c r="J75" s="26"/>
+      <c r="J75" s="25"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="28"/>
+      <c r="A76" s="27"/>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18"/>
       <c r="H76" s="4" t="s">
         <v>32</v>
       </c>
       <c r="I76" s="8">
         <v>6</v>
       </c>
-      <c r="J76" s="21"/>
+      <c r="J76" s="20"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="28"/>
+      <c r="A77" s="27"/>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="18" t="s">
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G77" s="18" t="s">
+      <c r="G77" s="17" t="s">
         <v>66</v>
       </c>
       <c r="H77" s="4" t="s">
@@ -3948,68 +3952,68 @@
       <c r="I77" s="8">
         <v>5</v>
       </c>
-      <c r="J77" s="20">
+      <c r="J77" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="28"/>
+      <c r="A78" s="27"/>
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
       <c r="H78" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I78" s="8">
         <v>11</v>
       </c>
-      <c r="J78" s="26"/>
+      <c r="J78" s="25"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="28"/>
+      <c r="A79" s="27"/>
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
       <c r="H79" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I79" s="8">
         <v>11</v>
       </c>
-      <c r="J79" s="26"/>
+      <c r="J79" s="25"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="28"/>
+      <c r="A80" s="27"/>
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
       <c r="H80" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I80" s="8">
         <v>24</v>
       </c>
-      <c r="J80" s="21"/>
+      <c r="J80" s="20"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="28"/>
+      <c r="A81" s="27"/>
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="18" t="s">
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="G81" s="18" t="s">
+      <c r="G81" s="17" t="s">
         <v>68</v>
       </c>
       <c r="H81" s="4" t="s">
@@ -4018,52 +4022,52 @@
       <c r="I81" s="8">
         <v>8</v>
       </c>
-      <c r="J81" s="20">
+      <c r="J81" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="28"/>
+      <c r="A82" s="27"/>
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
-      <c r="D82" s="28"/>
-      <c r="E82" s="28"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="24"/>
       <c r="H82" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I82" s="8">
         <v>36</v>
       </c>
-      <c r="J82" s="26"/>
+      <c r="J82" s="25"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="28"/>
+      <c r="A83" s="27"/>
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
-      <c r="D83" s="28"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
       <c r="H83" s="8">
         <v>216</v>
       </c>
       <c r="I83" s="8">
         <v>7</v>
       </c>
-      <c r="J83" s="21"/>
+      <c r="J83" s="20"/>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="28"/>
+      <c r="A84" s="27"/>
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="18" t="s">
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="G84" s="18" t="s">
+      <c r="G84" s="17" t="s">
         <v>69</v>
       </c>
       <c r="H84" s="8">
@@ -4072,52 +4076,52 @@
       <c r="I84" s="8">
         <v>17</v>
       </c>
-      <c r="J84" s="20">
+      <c r="J84" s="19">
         <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="28"/>
+      <c r="A85" s="27"/>
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
-      <c r="D85" s="28"/>
-      <c r="E85" s="28"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="25"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
       <c r="H85" s="8">
         <v>217</v>
       </c>
       <c r="I85" s="8">
         <v>24</v>
       </c>
-      <c r="J85" s="26"/>
+      <c r="J85" s="25"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="28"/>
+      <c r="A86" s="27"/>
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
-      <c r="D86" s="28"/>
-      <c r="E86" s="28"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
       <c r="H86" s="8">
         <v>218</v>
       </c>
       <c r="I86" s="8">
         <v>7</v>
       </c>
-      <c r="J86" s="21"/>
+      <c r="J86" s="20"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="28"/>
+      <c r="A87" s="27"/>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
-      <c r="D87" s="28"/>
-      <c r="E87" s="28"/>
-      <c r="F87" s="18" t="s">
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G87" s="18" t="s">
+      <c r="G87" s="17" t="s">
         <v>71</v>
       </c>
       <c r="H87" s="8">
@@ -4126,52 +4130,52 @@
       <c r="I87" s="8">
         <v>17</v>
       </c>
-      <c r="J87" s="20">
+      <c r="J87" s="19">
         <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="28"/>
+      <c r="A88" s="27"/>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
-      <c r="D88" s="28"/>
-      <c r="E88" s="28"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
       <c r="H88" s="8">
         <v>219</v>
       </c>
       <c r="I88" s="8">
         <v>24</v>
       </c>
-      <c r="J88" s="26"/>
+      <c r="J88" s="25"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="28"/>
+      <c r="A89" s="27"/>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
-      <c r="D89" s="28"/>
-      <c r="E89" s="28"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="19"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="18"/>
       <c r="H89" s="8">
         <v>220</v>
       </c>
       <c r="I89" s="8">
         <v>7</v>
       </c>
-      <c r="J89" s="21"/>
+      <c r="J89" s="20"/>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="28"/>
+      <c r="A90" s="27"/>
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="18" t="s">
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G90" s="18" t="s">
+      <c r="G90" s="17" t="s">
         <v>73</v>
       </c>
       <c r="H90" s="8">
@@ -4180,52 +4184,52 @@
       <c r="I90" s="8">
         <v>17</v>
       </c>
-      <c r="J90" s="20">
+      <c r="J90" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="28"/>
+      <c r="A91" s="27"/>
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="28"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
       <c r="H91" s="8">
         <v>221</v>
       </c>
       <c r="I91" s="8">
         <v>24</v>
       </c>
-      <c r="J91" s="26"/>
+      <c r="J91" s="25"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="28"/>
+      <c r="A92" s="27"/>
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
-      <c r="D92" s="28"/>
-      <c r="E92" s="28"/>
-      <c r="F92" s="19"/>
-      <c r="G92" s="19"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
       <c r="H92" s="8">
         <v>222</v>
       </c>
       <c r="I92" s="8">
         <v>10</v>
       </c>
-      <c r="J92" s="21"/>
+      <c r="J92" s="20"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="28"/>
+      <c r="A93" s="27"/>
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
-      <c r="D93" s="28"/>
-      <c r="E93" s="28"/>
-      <c r="F93" s="18" t="s">
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="G93" s="18" t="s">
+      <c r="G93" s="17" t="s">
         <v>75</v>
       </c>
       <c r="H93" s="8">
@@ -4234,52 +4238,52 @@
       <c r="I93" s="8">
         <v>14</v>
       </c>
-      <c r="J93" s="20">
+      <c r="J93" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="28"/>
+      <c r="A94" s="27"/>
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
-      <c r="D94" s="28"/>
-      <c r="E94" s="28"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
       <c r="H94" s="8">
         <v>223</v>
       </c>
       <c r="I94" s="8">
         <v>24</v>
       </c>
-      <c r="J94" s="26"/>
+      <c r="J94" s="25"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="28"/>
+      <c r="A95" s="27"/>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
-      <c r="D95" s="28"/>
-      <c r="E95" s="28"/>
-      <c r="F95" s="19"/>
-      <c r="G95" s="19"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="18"/>
       <c r="H95" s="8">
         <v>224</v>
       </c>
       <c r="I95" s="8">
         <v>13</v>
       </c>
-      <c r="J95" s="21"/>
+      <c r="J95" s="20"/>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="28"/>
+      <c r="A96" s="27"/>
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
-      <c r="D96" s="28"/>
-      <c r="E96" s="28"/>
-      <c r="F96" s="18" t="s">
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="G96" s="18" t="s">
+      <c r="G96" s="17" t="s">
         <v>76</v>
       </c>
       <c r="H96" s="8">
@@ -4288,48 +4292,48 @@
       <c r="I96" s="8">
         <v>11</v>
       </c>
-      <c r="J96" s="20">
+      <c r="J96" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="28"/>
+      <c r="A97" s="27"/>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
-      <c r="D97" s="28"/>
-      <c r="E97" s="28"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
       <c r="H97" s="8">
         <v>303</v>
       </c>
       <c r="I97" s="8">
         <v>24</v>
       </c>
-      <c r="J97" s="26"/>
+      <c r="J97" s="25"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="28"/>
+      <c r="A98" s="27"/>
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="28"/>
-      <c r="E98" s="28"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="18"/>
       <c r="H98" s="8">
         <v>304</v>
       </c>
       <c r="I98" s="8">
         <v>15</v>
       </c>
-      <c r="J98" s="21"/>
+      <c r="J98" s="20"/>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="29"/>
+      <c r="A99" s="28"/>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
-      <c r="D99" s="29"/>
-      <c r="E99" s="29"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
       <c r="F99" s="4" t="s">
         <v>72</v>
       </c>
@@ -4347,47 +4351,47 @@
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="27"/>
+      <c r="A100" s="26"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
-      <c r="D100" s="27"/>
-      <c r="E100" s="27"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="29"/>
+      <c r="G100" s="29"/>
       <c r="H100" s="8">
         <v>305</v>
       </c>
       <c r="I100" s="8">
         <v>24</v>
       </c>
-      <c r="J100" s="30"/>
+      <c r="J100" s="29"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="28"/>
+      <c r="A101" s="27"/>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="31"/>
-      <c r="G101" s="31"/>
+      <c r="D101" s="27"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
       <c r="H101" s="8">
         <v>306</v>
       </c>
       <c r="I101" s="8">
         <v>18</v>
       </c>
-      <c r="J101" s="31"/>
+      <c r="J101" s="30"/>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="28"/>
+      <c r="A102" s="27"/>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
-      <c r="D102" s="28"/>
-      <c r="E102" s="28"/>
-      <c r="F102" s="18" t="s">
+      <c r="D102" s="27"/>
+      <c r="E102" s="27"/>
+      <c r="F102" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G102" s="18" t="s">
+      <c r="G102" s="17" t="s">
         <v>78</v>
       </c>
       <c r="H102" s="8">
@@ -4396,52 +4400,52 @@
       <c r="I102" s="8">
         <v>6</v>
       </c>
-      <c r="J102" s="20">
+      <c r="J102" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="28"/>
+      <c r="A103" s="27"/>
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
-      <c r="D103" s="28"/>
-      <c r="E103" s="28"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
       <c r="H103" s="8">
         <v>307</v>
       </c>
       <c r="I103" s="8">
         <v>20</v>
       </c>
-      <c r="J103" s="26"/>
+      <c r="J103" s="25"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="28"/>
+      <c r="A104" s="27"/>
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
-      <c r="D104" s="28"/>
-      <c r="E104" s="28"/>
-      <c r="F104" s="19"/>
-      <c r="G104" s="19"/>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="18"/>
+      <c r="G104" s="18"/>
       <c r="H104" s="4" t="s">
         <v>51</v>
       </c>
       <c r="I104" s="8">
         <v>24</v>
       </c>
-      <c r="J104" s="21"/>
+      <c r="J104" s="20"/>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="28"/>
+      <c r="A105" s="27"/>
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
-      <c r="D105" s="28"/>
-      <c r="E105" s="28"/>
-      <c r="F105" s="18" t="s">
+      <c r="D105" s="27"/>
+      <c r="E105" s="27"/>
+      <c r="F105" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="G105" s="18" t="s">
+      <c r="G105" s="17" t="s">
         <v>80</v>
       </c>
       <c r="H105" s="4" t="s">
@@ -4450,36 +4454,36 @@
       <c r="I105" s="8">
         <v>24</v>
       </c>
-      <c r="J105" s="20">
+      <c r="J105" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="28"/>
+      <c r="A106" s="27"/>
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
-      <c r="D106" s="28"/>
-      <c r="E106" s="28"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="19"/>
+      <c r="D106" s="27"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="18"/>
+      <c r="G106" s="18"/>
       <c r="H106" s="8">
         <v>320</v>
       </c>
       <c r="I106" s="8">
         <v>27</v>
       </c>
-      <c r="J106" s="21"/>
+      <c r="J106" s="20"/>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="28"/>
+      <c r="A107" s="27"/>
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
-      <c r="D107" s="28"/>
-      <c r="E107" s="28"/>
-      <c r="F107" s="18" t="s">
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="G107" s="18" t="s">
+      <c r="G107" s="17" t="s">
         <v>81</v>
       </c>
       <c r="H107" s="8">
@@ -4488,54 +4492,54 @@
       <c r="I107" s="8">
         <v>4</v>
       </c>
-      <c r="J107" s="20">
+      <c r="J107" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="28"/>
+      <c r="A108" s="27"/>
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="28"/>
-      <c r="E108" s="28"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="25"/>
+      <c r="D108" s="27"/>
+      <c r="E108" s="27"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="24"/>
       <c r="H108" s="4" t="s">
         <v>57</v>
       </c>
       <c r="I108" s="8">
         <v>20</v>
       </c>
-      <c r="J108" s="26"/>
+      <c r="J108" s="25"/>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="29"/>
+      <c r="A109" s="28"/>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
-      <c r="D109" s="29"/>
-      <c r="E109" s="29"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="19"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="28"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
       <c r="H109" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I109" s="8">
         <v>27</v>
       </c>
-      <c r="J109" s="21"/>
+      <c r="J109" s="20"/>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="22" t="s">
+      <c r="A110" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B110" s="23"/>
-      <c r="C110" s="23"/>
-      <c r="D110" s="23"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="23"/>
-      <c r="G110" s="23"/>
-      <c r="H110" s="23"/>
-      <c r="I110" s="24"/>
+      <c r="B110" s="22"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22"/>
+      <c r="G110" s="22"/>
+      <c r="H110" s="22"/>
+      <c r="I110" s="23"/>
       <c r="J110" s="8">
         <v>1561</v>
       </c>
@@ -4705,25 +4709,25 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="31">
         <v>46256</v>
       </c>
       <c r="C2" t="s">
         <v>170</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>87</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -4732,84 +4736,84 @@
       <c r="I2" s="8">
         <v>11</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A3" s="25"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="8">
         <v>11</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="25"/>
     </row>
     <row r="4" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A4" s="25"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="8">
         <v>11</v>
       </c>
-      <c r="J4" s="26"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A5" s="25"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
       <c r="H5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="8">
         <v>11</v>
       </c>
-      <c r="J5" s="26"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A6" s="25"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
       <c r="H6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="8">
         <v>7</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="20"/>
     </row>
     <row r="7" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A7" s="25"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="18" t="s">
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="17" t="s">
         <v>89</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -4818,100 +4822,100 @@
       <c r="I7" s="8">
         <v>4</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A8" s="25"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="8">
         <v>11</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="25"/>
     </row>
     <row r="9" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A9" s="25"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="8">
         <v>11</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="25"/>
     </row>
     <row r="10" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A10" s="25"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="8">
         <v>11</v>
       </c>
-      <c r="J10" s="26"/>
+      <c r="J10" s="25"/>
     </row>
     <row r="11" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A11" s="25"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="8">
         <v>11</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A12" s="25"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
       <c r="H12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I12" s="8">
         <v>3</v>
       </c>
-      <c r="J12" s="21"/>
+      <c r="J12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A13" s="25"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="18" t="s">
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="17" t="s">
         <v>91</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -4920,84 +4924,84 @@
       <c r="I13" s="8">
         <v>8</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A14" s="25"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="8">
         <v>11</v>
       </c>
-      <c r="J14" s="26"/>
+      <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A15" s="25"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I15" s="8">
         <v>11</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="25"/>
     </row>
     <row r="16" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A16" s="25"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I16" s="8">
         <v>11</v>
       </c>
-      <c r="J16" s="26"/>
+      <c r="J16" s="25"/>
     </row>
     <row r="17" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A17" s="25"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
       <c r="H17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="8">
         <v>10</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A18" s="25"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="18" t="s">
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="17" t="s">
         <v>93</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -5006,100 +5010,100 @@
       <c r="I18" s="8">
         <v>1</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A19" s="25"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I19" s="8">
         <v>11</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A20" s="25"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
       <c r="H20" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="8">
         <v>11</v>
       </c>
-      <c r="J20" s="26"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A21" s="25"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="8">
         <v>11</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A22" s="25"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="4" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="8">
         <v>11</v>
       </c>
-      <c r="J22" s="26"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A23" s="25"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I23" s="8">
         <v>6</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A24" s="25"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="18" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>94</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -5108,68 +5112,68 @@
       <c r="I24" s="8">
         <v>5</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A25" s="25"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="8">
         <v>11</v>
       </c>
-      <c r="J25" s="26"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A26" s="25"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
       <c r="H26" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I26" s="8">
         <v>32</v>
       </c>
-      <c r="J26" s="26"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A27" s="25"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
       <c r="H27" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I27" s="8">
         <v>3</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A28" s="25"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="18" t="s">
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="17" t="s">
         <v>96</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -5178,36 +5182,36 @@
       <c r="I28" s="8">
         <v>33</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A29" s="25"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
       <c r="H29" s="8">
         <v>208</v>
       </c>
       <c r="I29" s="8">
         <v>18</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A30" s="25"/>
+      <c r="A30" s="24"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="18" t="s">
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="17" t="s">
         <v>97</v>
       </c>
       <c r="H30" s="8">
@@ -5216,48 +5220,48 @@
       <c r="I30" s="8">
         <v>24</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A31" s="25"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
       <c r="H31" s="8">
         <v>216</v>
       </c>
       <c r="I31" s="8">
         <v>24</v>
       </c>
-      <c r="J31" s="26"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A32" s="25"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="8">
         <v>217</v>
       </c>
       <c r="I32" s="8">
         <v>3</v>
       </c>
-      <c r="J32" s="21"/>
+      <c r="J32" s="20"/>
     </row>
     <row r="33" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A33" s="19"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
       <c r="F33" s="4" t="s">
         <v>86</v>
       </c>
@@ -5275,47 +5279,47 @@
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="27"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
       <c r="H34" s="8">
         <v>218</v>
       </c>
       <c r="I34" s="8">
         <v>24</v>
       </c>
-      <c r="J34" s="30"/>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="28"/>
+      <c r="A35" s="27"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
       <c r="H35" s="8">
         <v>219</v>
       </c>
       <c r="I35" s="8">
         <v>6</v>
       </c>
-      <c r="J35" s="31"/>
+      <c r="J35" s="30"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="28"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="18" t="s">
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="17" t="s">
         <v>100</v>
       </c>
       <c r="H36" s="8">
@@ -5324,52 +5328,52 @@
       <c r="I36" s="8">
         <v>18</v>
       </c>
-      <c r="J36" s="20">
+      <c r="J36" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="28"/>
+      <c r="A37" s="27"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
       <c r="H37" s="8">
         <v>220</v>
       </c>
       <c r="I37" s="8">
         <v>24</v>
       </c>
-      <c r="J37" s="26"/>
+      <c r="J37" s="25"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="28"/>
+      <c r="A38" s="27"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
       <c r="H38" s="8">
         <v>221</v>
       </c>
       <c r="I38" s="8">
         <v>9</v>
       </c>
-      <c r="J38" s="21"/>
+      <c r="J38" s="20"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="28"/>
+      <c r="A39" s="27"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="18" t="s">
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="17" t="s">
         <v>102</v>
       </c>
       <c r="H39" s="8">
@@ -5378,52 +5382,52 @@
       <c r="I39" s="8">
         <v>15</v>
       </c>
-      <c r="J39" s="20">
+      <c r="J39" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="28"/>
+      <c r="A40" s="27"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
       <c r="H40" s="8">
         <v>222</v>
       </c>
       <c r="I40" s="8">
         <v>24</v>
       </c>
-      <c r="J40" s="26"/>
+      <c r="J40" s="25"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="28"/>
+      <c r="A41" s="27"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
       <c r="H41" s="8">
         <v>223</v>
       </c>
       <c r="I41" s="8">
         <v>12</v>
       </c>
-      <c r="J41" s="21"/>
+      <c r="J41" s="20"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="28"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="18" t="s">
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="17" t="s">
         <v>103</v>
       </c>
       <c r="H42" s="8">
@@ -5432,52 +5436,52 @@
       <c r="I42" s="8">
         <v>12</v>
       </c>
-      <c r="J42" s="20">
+      <c r="J42" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="28"/>
+      <c r="A43" s="27"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
       <c r="H43" s="8">
         <v>224</v>
       </c>
       <c r="I43" s="8">
         <v>24</v>
       </c>
-      <c r="J43" s="26"/>
+      <c r="J43" s="25"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="28"/>
+      <c r="A44" s="27"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
       <c r="H44" s="8">
         <v>303</v>
       </c>
       <c r="I44" s="8">
         <v>15</v>
       </c>
-      <c r="J44" s="21"/>
+      <c r="J44" s="20"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="28"/>
+      <c r="A45" s="27"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="18" t="s">
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="17" t="s">
         <v>105</v>
       </c>
       <c r="H45" s="8">
@@ -5486,58 +5490,58 @@
       <c r="I45" s="8">
         <v>9</v>
       </c>
-      <c r="J45" s="20">
+      <c r="J45" s="19">
         <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="28"/>
+      <c r="A46" s="27"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
       <c r="H46" s="8">
         <v>304</v>
       </c>
       <c r="I46" s="8">
         <v>24</v>
       </c>
-      <c r="J46" s="26"/>
+      <c r="J46" s="25"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="29"/>
+      <c r="A47" s="28"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
       <c r="H47" s="8">
         <v>305</v>
       </c>
       <c r="I47" s="8">
         <v>5</v>
       </c>
-      <c r="J47" s="21"/>
+      <c r="J47" s="20"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F48" s="18" t="s">
+      <c r="F48" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G48" s="17" t="s">
         <v>109</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -5546,68 +5550,68 @@
       <c r="I48" s="8">
         <v>14</v>
       </c>
-      <c r="J48" s="20">
+      <c r="J48" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="25"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
       <c r="H49" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I49" s="8">
         <v>14</v>
       </c>
-      <c r="J49" s="26"/>
+      <c r="J49" s="25"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="25"/>
+      <c r="A50" s="24"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
       <c r="H50" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I50" s="8">
         <v>14</v>
       </c>
-      <c r="J50" s="26"/>
+      <c r="J50" s="25"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="25"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
       <c r="H51" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I51" s="8">
         <v>9</v>
       </c>
-      <c r="J51" s="21"/>
+      <c r="J51" s="20"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="25"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="18" t="s">
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G52" s="18" t="s">
+      <c r="G52" s="17" t="s">
         <v>110</v>
       </c>
       <c r="H52" s="4" t="s">
@@ -5616,84 +5620,84 @@
       <c r="I52" s="8">
         <v>5</v>
       </c>
-      <c r="J52" s="20">
+      <c r="J52" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="25"/>
+      <c r="A53" s="24"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
       <c r="H53" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="8">
         <v>14</v>
       </c>
-      <c r="J53" s="26"/>
+      <c r="J53" s="25"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="25"/>
+      <c r="A54" s="24"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
       <c r="H54" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I54" s="8">
         <v>14</v>
       </c>
-      <c r="J54" s="26"/>
+      <c r="J54" s="25"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="25"/>
+      <c r="A55" s="24"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
       <c r="H55" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I55" s="8">
         <v>14</v>
       </c>
-      <c r="J55" s="26"/>
+      <c r="J55" s="25"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="25"/>
+      <c r="A56" s="24"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
       <c r="H56" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I56" s="8">
         <v>3</v>
       </c>
-      <c r="J56" s="21"/>
+      <c r="J56" s="20"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="25"/>
+      <c r="A57" s="24"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="18" t="s">
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G57" s="18" t="s">
+      <c r="G57" s="17" t="s">
         <v>112</v>
       </c>
       <c r="H57" s="4" t="s">
@@ -5702,68 +5706,68 @@
       <c r="I57" s="8">
         <v>11</v>
       </c>
-      <c r="J57" s="20">
+      <c r="J57" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="25"/>
+      <c r="A58" s="24"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
       <c r="H58" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I58" s="8">
         <v>14</v>
       </c>
-      <c r="J58" s="26"/>
+      <c r="J58" s="25"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="25"/>
+      <c r="A59" s="24"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
       <c r="H59" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I59" s="8">
         <v>14</v>
       </c>
-      <c r="J59" s="26"/>
+      <c r="J59" s="25"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="25"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
       <c r="H60" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I60" s="8">
         <v>12</v>
       </c>
-      <c r="J60" s="21"/>
+      <c r="J60" s="20"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="25"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="18" t="s">
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G61" s="18" t="s">
+      <c r="G61" s="17" t="s">
         <v>113</v>
       </c>
       <c r="H61" s="4" t="s">
@@ -5772,80 +5776,80 @@
       <c r="I61" s="8">
         <v>2</v>
       </c>
-      <c r="J61" s="20">
+      <c r="J61" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="25"/>
+      <c r="A62" s="24"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
       <c r="H62" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I62" s="8">
         <v>14</v>
       </c>
-      <c r="J62" s="26"/>
+      <c r="J62" s="25"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="25"/>
+      <c r="A63" s="24"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
       <c r="H63" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I63" s="8">
         <v>14</v>
       </c>
-      <c r="J63" s="26"/>
+      <c r="J63" s="25"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="25"/>
+      <c r="A64" s="24"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
       <c r="H64" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I64" s="8">
         <v>14</v>
       </c>
-      <c r="J64" s="26"/>
+      <c r="J64" s="25"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="25"/>
+      <c r="A65" s="24"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
       <c r="H65" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I65" s="8">
         <v>7</v>
       </c>
-      <c r="J65" s="21"/>
+      <c r="J65" s="20"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="19"/>
+      <c r="A66" s="18"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
       <c r="F66" s="4" t="s">
         <v>114</v>
       </c>
@@ -5863,79 +5867,79 @@
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="27"/>
+      <c r="A67" s="26"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
       <c r="H67" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I67" s="8">
         <v>14</v>
       </c>
-      <c r="J67" s="27"/>
+      <c r="J67" s="26"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="28"/>
+      <c r="A68" s="27"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
       <c r="H68" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="8">
         <v>14</v>
       </c>
-      <c r="J68" s="28"/>
+      <c r="J68" s="27"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="28"/>
+      <c r="A69" s="27"/>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
       <c r="H69" s="4" t="s">
         <v>32</v>
       </c>
       <c r="I69" s="8">
         <v>14</v>
       </c>
-      <c r="J69" s="28"/>
+      <c r="J69" s="27"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="28"/>
+      <c r="A70" s="27"/>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
       <c r="H70" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I70" s="8">
         <v>2</v>
       </c>
-      <c r="J70" s="29"/>
+      <c r="J70" s="28"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="28"/>
+      <c r="A71" s="27"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="18" t="s">
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="17" t="s">
         <v>116</v>
       </c>
       <c r="H71" s="4" t="s">
@@ -5944,52 +5948,52 @@
       <c r="I71" s="8">
         <v>12</v>
       </c>
-      <c r="J71" s="20">
+      <c r="J71" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="28"/>
+      <c r="A72" s="27"/>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
       <c r="H72" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I72" s="8">
         <v>14</v>
       </c>
-      <c r="J72" s="26"/>
+      <c r="J72" s="25"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="28"/>
+      <c r="A73" s="27"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
       <c r="H73" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I73" s="8">
         <v>25</v>
       </c>
-      <c r="J73" s="21"/>
+      <c r="J73" s="20"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="28"/>
+      <c r="A74" s="27"/>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="18" t="s">
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="G74" s="17" t="s">
         <v>117</v>
       </c>
       <c r="H74" s="4" t="s">
@@ -5998,36 +6002,36 @@
       <c r="I74" s="8">
         <v>15</v>
       </c>
-      <c r="J74" s="20">
+      <c r="J74" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="28"/>
+      <c r="A75" s="27"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="19"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
       <c r="H75" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I75" s="8">
         <v>35</v>
       </c>
-      <c r="J75" s="21"/>
+      <c r="J75" s="20"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="28"/>
+      <c r="A76" s="27"/>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="18" t="s">
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G76" s="18" t="s">
+      <c r="G76" s="17" t="s">
         <v>118</v>
       </c>
       <c r="H76" s="4" t="s">
@@ -6036,52 +6040,52 @@
       <c r="I76" s="8">
         <v>1</v>
       </c>
-      <c r="J76" s="20">
+      <c r="J76" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="28"/>
+      <c r="A77" s="27"/>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
       <c r="H77" s="8">
         <v>208</v>
       </c>
       <c r="I77" s="8">
         <v>27</v>
       </c>
-      <c r="J77" s="26"/>
+      <c r="J77" s="25"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="28"/>
+      <c r="A78" s="27"/>
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
       <c r="H78" s="8">
         <v>213</v>
       </c>
       <c r="I78" s="8">
         <v>22</v>
       </c>
-      <c r="J78" s="21"/>
+      <c r="J78" s="20"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="28"/>
+      <c r="A79" s="27"/>
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="18" t="s">
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="G79" s="17" t="s">
         <v>119</v>
       </c>
       <c r="H79" s="8">
@@ -6090,68 +6094,68 @@
       <c r="I79" s="8">
         <v>2</v>
       </c>
-      <c r="J79" s="20">
+      <c r="J79" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="28"/>
+      <c r="A80" s="27"/>
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
       <c r="H80" s="8">
         <v>216</v>
       </c>
       <c r="I80" s="8">
         <v>24</v>
       </c>
-      <c r="J80" s="26"/>
+      <c r="J80" s="25"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="28"/>
+      <c r="A81" s="27"/>
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="25"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="24"/>
       <c r="H81" s="8">
         <v>217</v>
       </c>
       <c r="I81" s="8">
         <v>24</v>
       </c>
-      <c r="J81" s="26"/>
+      <c r="J81" s="25"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="28"/>
+      <c r="A82" s="27"/>
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
-      <c r="D82" s="28"/>
-      <c r="E82" s="28"/>
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18"/>
       <c r="H82" s="8">
         <v>218</v>
       </c>
       <c r="I82" s="8">
         <v>1</v>
       </c>
-      <c r="J82" s="21"/>
+      <c r="J82" s="20"/>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="28"/>
+      <c r="A83" s="27"/>
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
-      <c r="D83" s="28"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="18" t="s">
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="G83" s="18" t="s">
+      <c r="G83" s="17" t="s">
         <v>120</v>
       </c>
       <c r="H83" s="8">
@@ -6160,52 +6164,52 @@
       <c r="I83" s="8">
         <v>23</v>
       </c>
-      <c r="J83" s="20">
+      <c r="J83" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="28"/>
+      <c r="A84" s="27"/>
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
       <c r="H84" s="8">
         <v>219</v>
       </c>
       <c r="I84" s="8">
         <v>24</v>
       </c>
-      <c r="J84" s="26"/>
+      <c r="J84" s="25"/>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="28"/>
+      <c r="A85" s="27"/>
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
-      <c r="D85" s="28"/>
-      <c r="E85" s="28"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="18"/>
       <c r="H85" s="8">
         <v>220</v>
       </c>
       <c r="I85" s="8">
         <v>4</v>
       </c>
-      <c r="J85" s="21"/>
+      <c r="J85" s="20"/>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="28"/>
+      <c r="A86" s="27"/>
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
-      <c r="D86" s="28"/>
-      <c r="E86" s="28"/>
-      <c r="F86" s="18" t="s">
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="G86" s="18" t="s">
+      <c r="G86" s="17" t="s">
         <v>122</v>
       </c>
       <c r="H86" s="8">
@@ -6214,52 +6218,52 @@
       <c r="I86" s="8">
         <v>20</v>
       </c>
-      <c r="J86" s="20">
+      <c r="J86" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="28"/>
+      <c r="A87" s="27"/>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
-      <c r="D87" s="28"/>
-      <c r="E87" s="28"/>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="24"/>
       <c r="H87" s="8">
         <v>221</v>
       </c>
       <c r="I87" s="8">
         <v>24</v>
       </c>
-      <c r="J87" s="26"/>
+      <c r="J87" s="25"/>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="28"/>
+      <c r="A88" s="27"/>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
-      <c r="D88" s="28"/>
-      <c r="E88" s="28"/>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="18"/>
       <c r="H88" s="8">
         <v>222</v>
       </c>
       <c r="I88" s="8">
         <v>7</v>
       </c>
-      <c r="J88" s="21"/>
+      <c r="J88" s="20"/>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="28"/>
+      <c r="A89" s="27"/>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
-      <c r="D89" s="28"/>
-      <c r="E89" s="28"/>
-      <c r="F89" s="18" t="s">
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="G89" s="18" t="s">
+      <c r="G89" s="17" t="s">
         <v>123</v>
       </c>
       <c r="H89" s="8">
@@ -6268,52 +6272,52 @@
       <c r="I89" s="8">
         <v>17</v>
       </c>
-      <c r="J89" s="20">
+      <c r="J89" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="28"/>
+      <c r="A90" s="27"/>
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="24"/>
+      <c r="G90" s="24"/>
       <c r="H90" s="8">
         <v>223</v>
       </c>
       <c r="I90" s="8">
         <v>24</v>
       </c>
-      <c r="J90" s="26"/>
+      <c r="J90" s="25"/>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="28"/>
+      <c r="A91" s="27"/>
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="28"/>
-      <c r="F91" s="19"/>
-      <c r="G91" s="19"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="18"/>
       <c r="H91" s="8">
         <v>224</v>
       </c>
       <c r="I91" s="8">
         <v>10</v>
       </c>
-      <c r="J91" s="21"/>
+      <c r="J91" s="20"/>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="28"/>
+      <c r="A92" s="27"/>
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
-      <c r="D92" s="28"/>
-      <c r="E92" s="28"/>
-      <c r="F92" s="18" t="s">
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G92" s="18" t="s">
+      <c r="G92" s="17" t="s">
         <v>124</v>
       </c>
       <c r="H92" s="8">
@@ -6322,52 +6326,52 @@
       <c r="I92" s="8">
         <v>14</v>
       </c>
-      <c r="J92" s="20">
+      <c r="J92" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="28"/>
+      <c r="A93" s="27"/>
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
-      <c r="D93" s="28"/>
-      <c r="E93" s="28"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
       <c r="H93" s="8">
         <v>303</v>
       </c>
       <c r="I93" s="8">
         <v>24</v>
       </c>
-      <c r="J93" s="26"/>
+      <c r="J93" s="25"/>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="28"/>
+      <c r="A94" s="27"/>
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
-      <c r="D94" s="28"/>
-      <c r="E94" s="28"/>
-      <c r="F94" s="19"/>
-      <c r="G94" s="19"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
       <c r="H94" s="8">
         <v>304</v>
       </c>
       <c r="I94" s="8">
         <v>13</v>
       </c>
-      <c r="J94" s="21"/>
+      <c r="J94" s="20"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="28"/>
+      <c r="A95" s="27"/>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
-      <c r="D95" s="28"/>
-      <c r="E95" s="28"/>
-      <c r="F95" s="18" t="s">
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G95" s="18" t="s">
+      <c r="G95" s="17" t="s">
         <v>125</v>
       </c>
       <c r="H95" s="8">
@@ -6376,52 +6380,52 @@
       <c r="I95" s="8">
         <v>11</v>
       </c>
-      <c r="J95" s="20">
+      <c r="J95" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="28"/>
+      <c r="A96" s="27"/>
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
-      <c r="D96" s="28"/>
-      <c r="E96" s="28"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
       <c r="H96" s="8">
         <v>305</v>
       </c>
       <c r="I96" s="8">
         <v>24</v>
       </c>
-      <c r="J96" s="26"/>
+      <c r="J96" s="25"/>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="28"/>
+      <c r="A97" s="27"/>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
-      <c r="D97" s="28"/>
-      <c r="E97" s="28"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="18"/>
       <c r="H97" s="8">
         <v>306</v>
       </c>
       <c r="I97" s="8">
         <v>16</v>
       </c>
-      <c r="J97" s="21"/>
+      <c r="J97" s="20"/>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="28"/>
+      <c r="A98" s="27"/>
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="28"/>
-      <c r="E98" s="28"/>
-      <c r="F98" s="18" t="s">
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G98" s="18" t="s">
+      <c r="G98" s="17" t="s">
         <v>127</v>
       </c>
       <c r="H98" s="8">
@@ -6430,32 +6434,32 @@
       <c r="I98" s="8">
         <v>8</v>
       </c>
-      <c r="J98" s="20">
+      <c r="J98" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="29"/>
+      <c r="A99" s="28"/>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
-      <c r="D99" s="29"/>
-      <c r="E99" s="29"/>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="18"/>
       <c r="H99" s="8">
         <v>307</v>
       </c>
       <c r="I99" s="8">
         <v>28</v>
       </c>
-      <c r="J99" s="21"/>
+      <c r="J99" s="20"/>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="27"/>
+      <c r="A100" s="26"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
-      <c r="D100" s="27"/>
-      <c r="E100" s="27"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="4" t="s">
@@ -6467,15 +6471,15 @@
       <c r="J100" s="12"/>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="28"/>
+      <c r="A101" s="27"/>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="18" t="s">
+      <c r="D101" s="27"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G101" s="18" t="s">
+      <c r="G101" s="17" t="s">
         <v>128</v>
       </c>
       <c r="H101" s="4" t="s">
@@ -6484,52 +6488,52 @@
       <c r="I101" s="8">
         <v>9</v>
       </c>
-      <c r="J101" s="20">
+      <c r="J101" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="28"/>
+      <c r="A102" s="27"/>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
-      <c r="D102" s="28"/>
-      <c r="E102" s="28"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
+      <c r="D102" s="27"/>
+      <c r="E102" s="27"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
       <c r="H102" s="4" t="s">
         <v>54</v>
       </c>
       <c r="I102" s="8">
         <v>24</v>
       </c>
-      <c r="J102" s="26"/>
+      <c r="J102" s="25"/>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="28"/>
+      <c r="A103" s="27"/>
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
-      <c r="D103" s="28"/>
-      <c r="E103" s="28"/>
-      <c r="F103" s="19"/>
-      <c r="G103" s="19"/>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="18"/>
+      <c r="G103" s="18"/>
       <c r="H103" s="8">
         <v>320</v>
       </c>
       <c r="I103" s="8">
         <v>18</v>
       </c>
-      <c r="J103" s="21"/>
+      <c r="J103" s="20"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="28"/>
+      <c r="A104" s="27"/>
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
-      <c r="D104" s="28"/>
-      <c r="E104" s="28"/>
-      <c r="F104" s="18" t="s">
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="G104" s="18" t="s">
+      <c r="G104" s="17" t="s">
         <v>129</v>
       </c>
       <c r="H104" s="8">
@@ -6538,36 +6542,36 @@
       <c r="I104" s="8">
         <v>29</v>
       </c>
-      <c r="J104" s="20">
+      <c r="J104" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="28"/>
+      <c r="A105" s="27"/>
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
-      <c r="D105" s="28"/>
-      <c r="E105" s="28"/>
-      <c r="F105" s="19"/>
-      <c r="G105" s="19"/>
+      <c r="D105" s="27"/>
+      <c r="E105" s="27"/>
+      <c r="F105" s="18"/>
+      <c r="G105" s="18"/>
       <c r="H105" s="4" t="s">
         <v>57</v>
       </c>
       <c r="I105" s="8">
         <v>21</v>
       </c>
-      <c r="J105" s="21"/>
+      <c r="J105" s="20"/>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="28"/>
+      <c r="A106" s="27"/>
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
-      <c r="D106" s="28"/>
-      <c r="E106" s="28"/>
-      <c r="F106" s="18" t="s">
+      <c r="D106" s="27"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="G106" s="18" t="s">
+      <c r="G106" s="17" t="s">
         <v>130</v>
       </c>
       <c r="H106" s="4" t="s">
@@ -6576,52 +6580,52 @@
       <c r="I106" s="8">
         <v>4</v>
       </c>
-      <c r="J106" s="20">
+      <c r="J106" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="28"/>
+      <c r="A107" s="27"/>
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
-      <c r="D107" s="28"/>
-      <c r="E107" s="28"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
       <c r="H107" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I107" s="8">
         <v>25</v>
       </c>
-      <c r="J107" s="26"/>
+      <c r="J107" s="25"/>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="28"/>
+      <c r="A108" s="27"/>
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="28"/>
-      <c r="E108" s="28"/>
-      <c r="F108" s="19"/>
-      <c r="G108" s="19"/>
+      <c r="D108" s="27"/>
+      <c r="E108" s="27"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
       <c r="H108" s="4" t="s">
         <v>131</v>
       </c>
       <c r="I108" s="8">
         <v>22</v>
       </c>
-      <c r="J108" s="21"/>
+      <c r="J108" s="20"/>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="28"/>
+      <c r="A109" s="27"/>
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
-      <c r="D109" s="28"/>
-      <c r="E109" s="28"/>
-      <c r="F109" s="18" t="s">
+      <c r="D109" s="27"/>
+      <c r="E109" s="27"/>
+      <c r="F109" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G109" s="18" t="s">
+      <c r="G109" s="17" t="s">
         <v>132</v>
       </c>
       <c r="H109" s="4" t="s">
@@ -6630,52 +6634,52 @@
       <c r="I109" s="8">
         <v>3</v>
       </c>
-      <c r="J109" s="20">
+      <c r="J109" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="28"/>
+      <c r="A110" s="27"/>
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
-      <c r="D110" s="28"/>
-      <c r="E110" s="28"/>
-      <c r="F110" s="25"/>
-      <c r="G110" s="25"/>
+      <c r="D110" s="27"/>
+      <c r="E110" s="27"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="24"/>
       <c r="H110" s="4" t="s">
         <v>133</v>
       </c>
       <c r="I110" s="8">
         <v>25</v>
       </c>
-      <c r="J110" s="26"/>
+      <c r="J110" s="25"/>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="28"/>
+      <c r="A111" s="27"/>
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
-      <c r="D111" s="28"/>
-      <c r="E111" s="28"/>
-      <c r="F111" s="19"/>
-      <c r="G111" s="19"/>
+      <c r="D111" s="27"/>
+      <c r="E111" s="27"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
       <c r="H111" s="4" t="s">
         <v>134</v>
       </c>
       <c r="I111" s="8">
         <v>23</v>
       </c>
-      <c r="J111" s="21"/>
+      <c r="J111" s="20"/>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="28"/>
+      <c r="A112" s="27"/>
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="28"/>
-      <c r="E112" s="28"/>
-      <c r="F112" s="18" t="s">
+      <c r="D112" s="27"/>
+      <c r="E112" s="27"/>
+      <c r="F112" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G112" s="18" t="s">
+      <c r="G112" s="17" t="s">
         <v>135</v>
       </c>
       <c r="H112" s="4" t="s">
@@ -6684,52 +6688,52 @@
       <c r="I112" s="8">
         <v>2</v>
       </c>
-      <c r="J112" s="20">
+      <c r="J112" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="28"/>
+      <c r="A113" s="27"/>
       <c r="B113" s="10"/>
       <c r="C113" s="10"/>
-      <c r="D113" s="28"/>
-      <c r="E113" s="28"/>
-      <c r="F113" s="25"/>
-      <c r="G113" s="25"/>
+      <c r="D113" s="27"/>
+      <c r="E113" s="27"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
       <c r="H113" s="4" t="s">
         <v>136</v>
       </c>
       <c r="I113" s="8">
         <v>25</v>
       </c>
-      <c r="J113" s="26"/>
+      <c r="J113" s="25"/>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="28"/>
+      <c r="A114" s="27"/>
       <c r="B114" s="10"/>
       <c r="C114" s="10"/>
-      <c r="D114" s="28"/>
-      <c r="E114" s="28"/>
-      <c r="F114" s="19"/>
-      <c r="G114" s="19"/>
+      <c r="D114" s="27"/>
+      <c r="E114" s="27"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
       <c r="H114" s="8">
         <v>514</v>
       </c>
       <c r="I114" s="8">
         <v>24</v>
       </c>
-      <c r="J114" s="21"/>
+      <c r="J114" s="20"/>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="28"/>
+      <c r="A115" s="27"/>
       <c r="B115" s="10"/>
       <c r="C115" s="10"/>
-      <c r="D115" s="28"/>
-      <c r="E115" s="28"/>
-      <c r="F115" s="18" t="s">
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="G115" s="18" t="s">
+      <c r="G115" s="17" t="s">
         <v>137</v>
       </c>
       <c r="H115" s="8">
@@ -6738,52 +6742,52 @@
       <c r="I115" s="8">
         <v>24</v>
       </c>
-      <c r="J115" s="20">
+      <c r="J115" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="28"/>
+      <c r="A116" s="27"/>
       <c r="B116" s="10"/>
       <c r="C116" s="10"/>
-      <c r="D116" s="28"/>
-      <c r="E116" s="28"/>
-      <c r="F116" s="25"/>
-      <c r="G116" s="25"/>
+      <c r="D116" s="27"/>
+      <c r="E116" s="27"/>
+      <c r="F116" s="24"/>
+      <c r="G116" s="24"/>
       <c r="H116" s="8">
         <v>516</v>
       </c>
       <c r="I116" s="8">
         <v>24</v>
       </c>
-      <c r="J116" s="26"/>
+      <c r="J116" s="25"/>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="28"/>
+      <c r="A117" s="27"/>
       <c r="B117" s="10"/>
       <c r="C117" s="10"/>
-      <c r="D117" s="28"/>
-      <c r="E117" s="28"/>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19"/>
+      <c r="D117" s="27"/>
+      <c r="E117" s="27"/>
+      <c r="F117" s="18"/>
+      <c r="G117" s="18"/>
       <c r="H117" s="4" t="s">
         <v>138</v>
       </c>
       <c r="I117" s="8">
         <v>3</v>
       </c>
-      <c r="J117" s="21"/>
+      <c r="J117" s="20"/>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="28"/>
+      <c r="A118" s="27"/>
       <c r="B118" s="10"/>
       <c r="C118" s="10"/>
-      <c r="D118" s="28"/>
-      <c r="E118" s="28"/>
-      <c r="F118" s="18" t="s">
+      <c r="D118" s="27"/>
+      <c r="E118" s="27"/>
+      <c r="F118" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G118" s="18" t="s">
+      <c r="G118" s="17" t="s">
         <v>139</v>
       </c>
       <c r="H118" s="4" t="s">
@@ -6792,38 +6796,38 @@
       <c r="I118" s="8">
         <v>21</v>
       </c>
-      <c r="J118" s="20">
+      <c r="J118" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="29"/>
+      <c r="A119" s="28"/>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
-      <c r="D119" s="29"/>
-      <c r="E119" s="29"/>
-      <c r="F119" s="19"/>
-      <c r="G119" s="19"/>
+      <c r="D119" s="28"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="18"/>
+      <c r="G119" s="18"/>
       <c r="H119" s="8">
         <v>518</v>
       </c>
       <c r="I119" s="8">
         <v>29</v>
       </c>
-      <c r="J119" s="21"/>
+      <c r="J119" s="20"/>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="22" t="s">
+      <c r="A120" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B120" s="23"/>
-      <c r="C120" s="23"/>
-      <c r="D120" s="23"/>
-      <c r="E120" s="23"/>
-      <c r="F120" s="23"/>
-      <c r="G120" s="23"/>
-      <c r="H120" s="23"/>
-      <c r="I120" s="24"/>
+      <c r="B120" s="22"/>
+      <c r="C120" s="22"/>
+      <c r="D120" s="22"/>
+      <c r="E120" s="22"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="22"/>
+      <c r="H120" s="22"/>
+      <c r="I120" s="23"/>
       <c r="J120" s="8">
         <v>1716</v>
       </c>
@@ -6885,13 +6889,6 @@
     <mergeCell ref="G57:G60"/>
     <mergeCell ref="J57:J60"/>
     <mergeCell ref="F61:F65"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="F79:F82"/>
-    <mergeCell ref="G79:G82"/>
-    <mergeCell ref="J79:J82"/>
-    <mergeCell ref="F83:F85"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="J83:J85"/>
     <mergeCell ref="G61:G65"/>
     <mergeCell ref="J61:J65"/>
     <mergeCell ref="F67:F70"/>
@@ -6903,13 +6900,6 @@
     <mergeCell ref="F74:F75"/>
     <mergeCell ref="G74:G75"/>
     <mergeCell ref="J74:J75"/>
-    <mergeCell ref="F76:F78"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="F92:F94"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="J92:J94"/>
-    <mergeCell ref="F95:F97"/>
-    <mergeCell ref="G95:G97"/>
     <mergeCell ref="J95:J97"/>
     <mergeCell ref="F86:F88"/>
     <mergeCell ref="G86:G88"/>
@@ -6917,6 +6907,15 @@
     <mergeCell ref="F89:F91"/>
     <mergeCell ref="G89:G91"/>
     <mergeCell ref="J89:J91"/>
+    <mergeCell ref="J76:J78"/>
+    <mergeCell ref="F79:F82"/>
+    <mergeCell ref="G79:G82"/>
+    <mergeCell ref="J79:J82"/>
+    <mergeCell ref="F83:F85"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="J83:J85"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="G76:G78"/>
     <mergeCell ref="F98:F99"/>
     <mergeCell ref="G98:G99"/>
     <mergeCell ref="J98:J99"/>
@@ -6936,6 +6935,11 @@
     <mergeCell ref="A67:A99"/>
     <mergeCell ref="D67:D99"/>
     <mergeCell ref="E67:E99"/>
+    <mergeCell ref="F92:F94"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="J92:J94"/>
+    <mergeCell ref="F95:F97"/>
+    <mergeCell ref="G95:G97"/>
     <mergeCell ref="A120:I120"/>
     <mergeCell ref="F115:F117"/>
     <mergeCell ref="G115:G117"/>
@@ -7003,25 +7007,25 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="31">
         <v>46256</v>
       </c>
       <c r="C2" t="s">
         <v>171</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>143</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -7030,68 +7034,68 @@
       <c r="I2" s="8">
         <v>14</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="19">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A3" s="25"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="8">
         <v>14</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="25"/>
     </row>
     <row r="4" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A4" s="25"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="8">
         <v>14</v>
       </c>
-      <c r="J4" s="26"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A5" s="25"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="8">
         <v>7</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A6" s="25"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="18" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>145</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -7100,84 +7104,84 @@
       <c r="I6" s="8">
         <v>7</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A7" s="25"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="8">
         <v>14</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="25"/>
     </row>
     <row r="8" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A8" s="25"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="8">
         <v>14</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="25"/>
     </row>
     <row r="9" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A9" s="25"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="8">
         <v>14</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="25"/>
     </row>
     <row r="10" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A10" s="25"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
       <c r="H10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="8">
         <v>1</v>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="20"/>
     </row>
     <row r="11" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A11" s="25"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="18" t="s">
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="17" t="s">
         <v>147</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -7186,68 +7190,68 @@
       <c r="I11" s="8">
         <v>13</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A12" s="25"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="8">
         <v>14</v>
       </c>
-      <c r="J12" s="26"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A13" s="25"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="8">
         <v>14</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A14" s="25"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
       <c r="H14" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="8">
         <v>10</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A15" s="25"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="18" t="s">
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="17" t="s">
         <v>148</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -7256,84 +7260,84 @@
       <c r="I15" s="8">
         <v>4</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A16" s="25"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="8">
         <v>14</v>
       </c>
-      <c r="J16" s="26"/>
+      <c r="J16" s="25"/>
     </row>
     <row r="17" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A17" s="25"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I17" s="8">
         <v>14</v>
       </c>
-      <c r="J17" s="26"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A18" s="25"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="8">
         <v>14</v>
       </c>
-      <c r="J18" s="26"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A19" s="25"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I19" s="8">
         <v>5</v>
       </c>
-      <c r="J19" s="21"/>
+      <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A20" s="25"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="18" t="s">
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="17" t="s">
         <v>149</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -7342,68 +7346,68 @@
       <c r="I20" s="8">
         <v>9</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A21" s="25"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="8">
         <v>14</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A22" s="25"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="8">
         <v>14</v>
       </c>
-      <c r="J22" s="26"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A23" s="25"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="4" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="8">
         <v>14</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A24" s="25"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="18" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>151</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -7412,52 +7416,52 @@
       <c r="I24" s="8">
         <v>14</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A25" s="25"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="8">
         <v>14</v>
       </c>
-      <c r="J25" s="26"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A26" s="25"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
       <c r="H26" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I26" s="8">
         <v>23</v>
       </c>
-      <c r="J26" s="21"/>
+      <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A27" s="25"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="18" t="s">
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="17" t="s">
         <v>152</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -7466,36 +7470,36 @@
       <c r="I27" s="8">
         <v>17</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A28" s="25"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
       <c r="H28" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="8">
         <v>34</v>
       </c>
-      <c r="J28" s="21"/>
+      <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A29" s="25"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="18" t="s">
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="17" t="s">
         <v>153</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -7504,64 +7508,64 @@
       <c r="I29" s="8">
         <v>2</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A30" s="25"/>
+      <c r="A30" s="24"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
       <c r="H30" s="8">
         <v>216</v>
       </c>
       <c r="I30" s="8">
         <v>24</v>
       </c>
-      <c r="J30" s="26"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A31" s="25"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
       <c r="H31" s="8">
         <v>217</v>
       </c>
       <c r="I31" s="8">
         <v>24</v>
       </c>
-      <c r="J31" s="26"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A32" s="25"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="8">
         <v>218</v>
       </c>
       <c r="I32" s="8">
         <v>1</v>
       </c>
-      <c r="J32" s="21"/>
+      <c r="J32" s="20"/>
     </row>
     <row r="33" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A33" s="19"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
       <c r="F33" s="4" t="s">
         <v>144</v>
       </c>
@@ -7579,47 +7583,47 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A34" s="27"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
       <c r="H34" s="8">
         <v>219</v>
       </c>
       <c r="I34" s="8">
         <v>24</v>
       </c>
-      <c r="J34" s="30"/>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A35" s="28"/>
+      <c r="A35" s="27"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
       <c r="H35" s="8">
         <v>220</v>
       </c>
       <c r="I35" s="8">
         <v>4</v>
       </c>
-      <c r="J35" s="31"/>
+      <c r="J35" s="30"/>
     </row>
     <row r="36" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A36" s="28"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="18" t="s">
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="17" t="s">
         <v>155</v>
       </c>
       <c r="H36" s="8">
@@ -7628,52 +7632,52 @@
       <c r="I36" s="8">
         <v>20</v>
       </c>
-      <c r="J36" s="20">
+      <c r="J36" s="19">
         <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A37" s="28"/>
+      <c r="A37" s="27"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
       <c r="H37" s="8">
         <v>221</v>
       </c>
       <c r="I37" s="8">
         <v>24</v>
       </c>
-      <c r="J37" s="26"/>
+      <c r="J37" s="25"/>
     </row>
     <row r="38" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A38" s="28"/>
+      <c r="A38" s="27"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
       <c r="H38" s="8">
         <v>222</v>
       </c>
       <c r="I38" s="8">
         <v>5</v>
       </c>
-      <c r="J38" s="21"/>
+      <c r="J38" s="20"/>
     </row>
     <row r="39" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A39" s="28"/>
+      <c r="A39" s="27"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="18" t="s">
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="17" t="s">
         <v>156</v>
       </c>
       <c r="H39" s="8">
@@ -7682,52 +7686,52 @@
       <c r="I39" s="8">
         <v>19</v>
       </c>
-      <c r="J39" s="20">
+      <c r="J39" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A40" s="28"/>
+      <c r="A40" s="27"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
       <c r="H40" s="8">
         <v>223</v>
       </c>
       <c r="I40" s="8">
         <v>24</v>
       </c>
-      <c r="J40" s="26"/>
+      <c r="J40" s="25"/>
     </row>
     <row r="41" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A41" s="28"/>
+      <c r="A41" s="27"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
       <c r="H41" s="8">
         <v>224</v>
       </c>
       <c r="I41" s="8">
         <v>8</v>
       </c>
-      <c r="J41" s="21"/>
+      <c r="J41" s="20"/>
     </row>
     <row r="42" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A42" s="28"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="18" t="s">
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="17" t="s">
         <v>158</v>
       </c>
       <c r="H42" s="8">
@@ -7736,52 +7740,52 @@
       <c r="I42" s="8">
         <v>16</v>
       </c>
-      <c r="J42" s="20">
+      <c r="J42" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A43" s="28"/>
+      <c r="A43" s="27"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
       <c r="H43" s="8">
         <v>303</v>
       </c>
       <c r="I43" s="8">
         <v>24</v>
       </c>
-      <c r="J43" s="26"/>
+      <c r="J43" s="25"/>
     </row>
     <row r="44" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A44" s="28"/>
+      <c r="A44" s="27"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
       <c r="H44" s="8">
         <v>304</v>
       </c>
       <c r="I44" s="8">
         <v>11</v>
       </c>
-      <c r="J44" s="21"/>
+      <c r="J44" s="20"/>
     </row>
     <row r="45" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A45" s="28"/>
+      <c r="A45" s="27"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="18" t="s">
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="17" t="s">
         <v>159</v>
       </c>
       <c r="H45" s="8">
@@ -7790,52 +7794,52 @@
       <c r="I45" s="8">
         <v>13</v>
       </c>
-      <c r="J45" s="20">
+      <c r="J45" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A46" s="28"/>
+      <c r="A46" s="27"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
       <c r="H46" s="8">
         <v>305</v>
       </c>
       <c r="I46" s="8">
         <v>24</v>
       </c>
-      <c r="J46" s="26"/>
+      <c r="J46" s="25"/>
     </row>
     <row r="47" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A47" s="28"/>
+      <c r="A47" s="27"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
       <c r="H47" s="8">
         <v>306</v>
       </c>
       <c r="I47" s="8">
         <v>14</v>
       </c>
-      <c r="J47" s="21"/>
+      <c r="J47" s="20"/>
     </row>
     <row r="48" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A48" s="28"/>
+      <c r="A48" s="27"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="18" t="s">
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G48" s="17" t="s">
         <v>160</v>
       </c>
       <c r="H48" s="8">
@@ -7844,52 +7848,52 @@
       <c r="I48" s="8">
         <v>10</v>
       </c>
-      <c r="J48" s="20">
+      <c r="J48" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A49" s="28"/>
+      <c r="A49" s="27"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
       <c r="H49" s="8">
         <v>307</v>
       </c>
       <c r="I49" s="8">
         <v>28</v>
       </c>
-      <c r="J49" s="26"/>
+      <c r="J49" s="25"/>
     </row>
     <row r="50" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A50" s="28"/>
+      <c r="A50" s="27"/>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
       <c r="H50" s="4" t="s">
         <v>51</v>
       </c>
       <c r="I50" s="8">
         <v>13</v>
       </c>
-      <c r="J50" s="21"/>
+      <c r="J50" s="20"/>
     </row>
     <row r="51" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A51" s="28"/>
+      <c r="A51" s="27"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="18" t="s">
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="G51" s="17" t="s">
         <v>161</v>
       </c>
       <c r="H51" s="4" t="s">
@@ -7898,52 +7902,52 @@
       <c r="I51" s="8">
         <v>11</v>
       </c>
-      <c r="J51" s="20">
+      <c r="J51" s="19">
         <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A52" s="28"/>
+      <c r="A52" s="27"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
       <c r="H52" s="4" t="s">
         <v>54</v>
       </c>
       <c r="I52" s="8">
         <v>24</v>
       </c>
-      <c r="J52" s="26"/>
+      <c r="J52" s="25"/>
     </row>
     <row r="53" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A53" s="28"/>
+      <c r="A53" s="27"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
       <c r="H53" s="8">
         <v>320</v>
       </c>
       <c r="I53" s="8">
         <v>16</v>
       </c>
-      <c r="J53" s="21"/>
+      <c r="J53" s="20"/>
     </row>
     <row r="54" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A54" s="28"/>
+      <c r="A54" s="27"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="18" t="s">
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="G54" s="18" t="s">
+      <c r="G54" s="17" t="s">
         <v>162</v>
       </c>
       <c r="H54" s="8">
@@ -7952,38 +7956,38 @@
       <c r="I54" s="8">
         <v>31</v>
       </c>
-      <c r="J54" s="20">
+      <c r="J54" s="19">
         <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A55" s="29"/>
+      <c r="A55" s="28"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
       <c r="H55" s="4" t="s">
         <v>57</v>
       </c>
       <c r="I55" s="8">
         <v>19</v>
       </c>
-      <c r="J55" s="21"/>
+      <c r="J55" s="20"/>
     </row>
     <row r="56" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="24"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="23"/>
       <c r="J56" s="8">
         <v>810</v>
       </c>
